--- a/Daily_Report/Top 7 broker List with its Turnover 2024-12-10.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-12-10.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="273">
   <si>
     <t>Date: 2024-12-10</t>
   </si>
@@ -68,18 +68,18 @@
     <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
   </si>
   <si>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
     <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
-    <t>Sani Securities Company Limited</t>
+    <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
     <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
   </si>
   <si>
-    <t>Trishakti Securities Public Limited</t>
-  </si>
-  <si>
     <t>58</t>
   </si>
   <si>
@@ -89,79 +89,79 @@
     <t>57</t>
   </si>
   <si>
+    <t>42</t>
+  </si>
+  <si>
     <t>34</t>
   </si>
   <si>
-    <t>42</t>
+    <t>49</t>
   </si>
   <si>
     <t>38</t>
   </si>
   <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>859,424,472.7</t>
-  </si>
-  <si>
-    <t>365,306,198.6</t>
-  </si>
-  <si>
-    <t>306,267,908.62</t>
-  </si>
-  <si>
-    <t>281,378,434.89</t>
-  </si>
-  <si>
-    <t>270,997,997.39</t>
-  </si>
-  <si>
-    <t>224,080,791.8</t>
-  </si>
-  <si>
-    <t>223,313,483.76</t>
-  </si>
-  <si>
-    <t>363,472,721.2</t>
-  </si>
-  <si>
-    <t>223,987,204.1</t>
-  </si>
-  <si>
-    <t>125,866,560.02</t>
-  </si>
-  <si>
-    <t>131,604,665.5</t>
-  </si>
-  <si>
-    <t>136,049,763.0</t>
-  </si>
-  <si>
-    <t>105,624,896.3</t>
-  </si>
-  <si>
-    <t>115,686,617.3</t>
-  </si>
-  <si>
-    <t>495,951,751.5</t>
-  </si>
-  <si>
-    <t>141,318,994.5</t>
-  </si>
-  <si>
-    <t>180,401,348.6</t>
-  </si>
-  <si>
-    <t>149,773,769.4</t>
-  </si>
-  <si>
-    <t>134,948,234.4</t>
-  </si>
-  <si>
-    <t>118,455,895.5</t>
-  </si>
-  <si>
-    <t>107,626,866.46</t>
+    <t>829,900,801.8</t>
+  </si>
+  <si>
+    <t>418,983,705.0</t>
+  </si>
+  <si>
+    <t>311,846,972.62</t>
+  </si>
+  <si>
+    <t>295,101,692.8</t>
+  </si>
+  <si>
+    <t>268,257,912.7</t>
+  </si>
+  <si>
+    <t>238,069,023.4</t>
+  </si>
+  <si>
+    <t>230,955,787.2</t>
+  </si>
+  <si>
+    <t>359,016,981.0</t>
+  </si>
+  <si>
+    <t>257,143,286.8</t>
+  </si>
+  <si>
+    <t>123,871,821.32</t>
+  </si>
+  <si>
+    <t>148,434,967.8</t>
+  </si>
+  <si>
+    <t>133,463,046.2</t>
+  </si>
+  <si>
+    <t>106,024,973.2</t>
+  </si>
+  <si>
+    <t>111,291,817.5</t>
+  </si>
+  <si>
+    <t>470,883,820.8</t>
+  </si>
+  <si>
+    <t>161,840,418.19</t>
+  </si>
+  <si>
+    <t>187,975,151.3</t>
+  </si>
+  <si>
+    <t>146,666,725.0</t>
+  </si>
+  <si>
+    <t>134,794,866.5</t>
+  </si>
+  <si>
+    <t>132,044,050.2</t>
+  </si>
+  <si>
+    <t>119,663,969.7</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,46 +182,37 @@
     <t>SBI</t>
   </si>
   <si>
-    <t>101,284,517.2</t>
+    <t>101,289,116.2</t>
   </si>
   <si>
     <t>NRN</t>
   </si>
   <si>
-    <t>35,626,886.4</t>
+    <t>35,087,034.9</t>
   </si>
   <si>
     <t>LICN</t>
   </si>
   <si>
-    <t>33,401,133.8</t>
+    <t>34,431,688.79</t>
   </si>
   <si>
     <t>SHIVM</t>
   </si>
   <si>
-    <t>11,277,212.0</t>
+    <t>11,418,012.0</t>
   </si>
   <si>
     <t>FMDBL</t>
   </si>
   <si>
-    <t>8,786,766.1</t>
+    <t>9,011,016.1</t>
   </si>
   <si>
     <t>SHPC</t>
   </si>
   <si>
-    <t>59,128,282.3</t>
-  </si>
-  <si>
-    <t>JOSHI</t>
-  </si>
-  <si>
-    <t>15,991,234.0</t>
-  </si>
-  <si>
-    <t>15,381,653.6</t>
+    <t>108,855,521.1</t>
   </si>
   <si>
     <t>PMLIP</t>
@@ -233,238 +224,265 @@
     <t>HDL</t>
   </si>
   <si>
-    <t>4,370,750.8</t>
+    <t>6,435,196.5</t>
+  </si>
+  <si>
+    <t>5,968,033.6</t>
+  </si>
+  <si>
+    <t>SLBSL</t>
+  </si>
+  <si>
+    <t>4,171,878.9</t>
+  </si>
+  <si>
+    <t>7,871,760.1</t>
+  </si>
+  <si>
+    <t>AKJCL</t>
+  </si>
+  <si>
+    <t>5,042,282.09</t>
   </si>
   <si>
     <t>MEL</t>
   </si>
   <si>
-    <t>14,512,897.5</t>
-  </si>
-  <si>
-    <t>5,319,042.09</t>
-  </si>
-  <si>
-    <t>AKJCL</t>
-  </si>
-  <si>
-    <t>5,042,282.09</t>
+    <t>4,509,409.5</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>3,164,811.5</t>
+  </si>
+  <si>
+    <t>3,041,111.7</t>
+  </si>
+  <si>
+    <t>SCB</t>
+  </si>
+  <si>
+    <t>8,377,153.8</t>
+  </si>
+  <si>
+    <t>5,186,835.4</t>
+  </si>
+  <si>
+    <t>4,254,248.0</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>3,502,194.0</t>
+  </si>
+  <si>
+    <t>MNBBL</t>
+  </si>
+  <si>
+    <t>3,232,396.2</t>
+  </si>
+  <si>
+    <t>11,718,451.7</t>
+  </si>
+  <si>
+    <t>KBL</t>
+  </si>
+  <si>
+    <t>4,937,244.4</t>
+  </si>
+  <si>
+    <t>4,799,577.09</t>
+  </si>
+  <si>
+    <t>SSHL</t>
+  </si>
+  <si>
+    <t>3,818,992.0</t>
+  </si>
+  <si>
+    <t>SAHAS</t>
+  </si>
+  <si>
+    <t>3,480,977.0</t>
+  </si>
+  <si>
+    <t>5,681,900.6</t>
+  </si>
+  <si>
+    <t>4,611,589.0</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>4,488,889.09</t>
+  </si>
+  <si>
+    <t>4,401,185.09</t>
+  </si>
+  <si>
+    <t>KPCL</t>
+  </si>
+  <si>
+    <t>2,935,555.0</t>
+  </si>
+  <si>
+    <t>11,456,689.7</t>
+  </si>
+  <si>
+    <t>KRBL</t>
+  </si>
+  <si>
+    <t>6,807,016.4</t>
+  </si>
+  <si>
+    <t>ENL</t>
+  </si>
+  <si>
+    <t>3,978,933.4</t>
+  </si>
+  <si>
+    <t>3,291,410.0</t>
+  </si>
+  <si>
+    <t>2,748,039.7</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>101,595,619.1</t>
+  </si>
+  <si>
+    <t>90,829,832.9</t>
+  </si>
+  <si>
+    <t>43,673,374.0</t>
+  </si>
+  <si>
+    <t>SNLI</t>
+  </si>
+  <si>
+    <t>41,248,644.6</t>
+  </si>
+  <si>
+    <t>RHPL</t>
+  </si>
+  <si>
+    <t>20,628,145.3</t>
+  </si>
+  <si>
+    <t>32,747,285.1</t>
+  </si>
+  <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>5,154,300.2</t>
+  </si>
+  <si>
+    <t>LBBL</t>
+  </si>
+  <si>
+    <t>4,767,617.59</t>
+  </si>
+  <si>
+    <t>JFL</t>
+  </si>
+  <si>
+    <t>4,587,360.5</t>
+  </si>
+  <si>
+    <t>DOLTI</t>
+  </si>
+  <si>
+    <t>2,379,534.0</t>
+  </si>
+  <si>
+    <t>50,898,255.6</t>
+  </si>
+  <si>
+    <t>6,824,240.0</t>
+  </si>
+  <si>
+    <t>RFPL</t>
+  </si>
+  <si>
+    <t>5,768,873.0</t>
+  </si>
+  <si>
+    <t>KKHC</t>
+  </si>
+  <si>
+    <t>3,466,701.5</t>
+  </si>
+  <si>
+    <t>3,402,317.2</t>
+  </si>
+  <si>
+    <t>13,668,522.4</t>
+  </si>
+  <si>
+    <t>10,999,386.1</t>
+  </si>
+  <si>
+    <t>SIKLES</t>
+  </si>
+  <si>
+    <t>7,813,264.0</t>
+  </si>
+  <si>
+    <t>6,862,741.8</t>
+  </si>
+  <si>
+    <t>4,419,829.9</t>
+  </si>
+  <si>
+    <t>6,976,596.4</t>
+  </si>
+  <si>
+    <t>4,546,853.59</t>
   </si>
   <si>
     <t>NGPL</t>
   </si>
   <si>
-    <t>3,466,149.5</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>3,051,311.9</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>11,788,268.7</t>
-  </si>
-  <si>
-    <t>7,279,927.1</t>
-  </si>
-  <si>
-    <t>KBL</t>
-  </si>
-  <si>
-    <t>4,891,389.4</t>
-  </si>
-  <si>
-    <t>SSHL</t>
-  </si>
-  <si>
-    <t>3,417,592.0</t>
-  </si>
-  <si>
-    <t>3,400,067.0</t>
-  </si>
-  <si>
-    <t>SCB</t>
-  </si>
-  <si>
-    <t>5,498,579.9</t>
-  </si>
-  <si>
-    <t>SLBSL</t>
-  </si>
-  <si>
-    <t>4,254,248.0</t>
-  </si>
-  <si>
-    <t>3,287,577.1</t>
-  </si>
-  <si>
-    <t>MNBBL</t>
-  </si>
-  <si>
-    <t>3,232,396.2</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>3,229,814.0</t>
-  </si>
-  <si>
-    <t>9,433,924.69</t>
-  </si>
-  <si>
-    <t>KRBL</t>
-  </si>
-  <si>
-    <t>6,807,016.4</t>
-  </si>
-  <si>
-    <t>ENL</t>
-  </si>
-  <si>
-    <t>3,911,818.4</t>
-  </si>
-  <si>
-    <t>3,373,424.0</t>
-  </si>
-  <si>
-    <t>2,776,269.5</t>
-  </si>
-  <si>
-    <t>14,500,222.8</t>
-  </si>
-  <si>
-    <t>SAHAS</t>
-  </si>
-  <si>
-    <t>9,466,048.5</t>
-  </si>
-  <si>
-    <t>8,138,097.4</t>
-  </si>
-  <si>
-    <t>SBL</t>
-  </si>
-  <si>
-    <t>5,894,267.0</t>
-  </si>
-  <si>
-    <t>3,990,531.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>114,296,079.7</t>
-  </si>
-  <si>
-    <t>101,595,619.1</t>
-  </si>
-  <si>
-    <t>43,465,989.9</t>
-  </si>
-  <si>
-    <t>SNLI</t>
-  </si>
-  <si>
-    <t>41,225,235.0</t>
-  </si>
-  <si>
-    <t>RHPL</t>
-  </si>
-  <si>
-    <t>20,536,765.8</t>
-  </si>
-  <si>
-    <t>9,762,921.0</t>
-  </si>
-  <si>
-    <t>GFCL</t>
-  </si>
-  <si>
-    <t>5,154,300.2</t>
-  </si>
-  <si>
-    <t>LBBL</t>
-  </si>
-  <si>
-    <t>4,767,617.59</t>
-  </si>
-  <si>
-    <t>4,532,220.5</t>
-  </si>
-  <si>
-    <t>RFPL</t>
-  </si>
-  <si>
-    <t>4,182,496.0</t>
-  </si>
-  <si>
-    <t>50,611,378.6</t>
-  </si>
-  <si>
-    <t>6,824,240.0</t>
-  </si>
-  <si>
-    <t>5,738,588.0</t>
-  </si>
-  <si>
-    <t>3,288,817.2</t>
-  </si>
-  <si>
-    <t>3,118,991.0</t>
-  </si>
-  <si>
-    <t>UPPER</t>
-  </si>
-  <si>
-    <t>9,331,375.5</t>
-  </si>
-  <si>
-    <t>9,112,121.0</t>
-  </si>
-  <si>
-    <t>6,870,096.4</t>
-  </si>
-  <si>
-    <t>4,546,853.59</t>
-  </si>
-  <si>
-    <t>3,334,713.9</t>
-  </si>
-  <si>
-    <t>10,123,913.6</t>
-  </si>
-  <si>
-    <t>SIKLES</t>
-  </si>
-  <si>
-    <t>7,813,264.0</t>
-  </si>
-  <si>
-    <t>6,754,325.3</t>
-  </si>
-  <si>
-    <t>4,419,829.9</t>
-  </si>
-  <si>
-    <t>DOLTI</t>
-  </si>
-  <si>
-    <t>3,972,946.0</t>
+    <t>3,685,928.4</t>
+  </si>
+  <si>
+    <t>3,398,208.2</t>
+  </si>
+  <si>
+    <t>2,931,699.0</t>
+  </si>
+  <si>
+    <t>SKBBL</t>
+  </si>
+  <si>
+    <t>6,819,467.1</t>
+  </si>
+  <si>
+    <t>6,745,992.0</t>
+  </si>
+  <si>
+    <t>4,748,702.8</t>
+  </si>
+  <si>
+    <t>4,443,872.3</t>
+  </si>
+  <si>
+    <t>3,565,936.6</t>
   </si>
   <si>
     <t>ILI</t>
   </si>
   <si>
-    <t>9,638,241.19</t>
-  </si>
-  <si>
-    <t>6,782,628.1</t>
+    <t>9,580,080.19</t>
+  </si>
+  <si>
+    <t>6,874,328.1</t>
   </si>
   <si>
     <t>5,183,371.3</t>
@@ -473,36 +491,12 @@
     <t>SHEL</t>
   </si>
   <si>
-    <t>3,583,083.7</t>
+    <t>3,684,362.7</t>
   </si>
   <si>
     <t>3,321,120.0</t>
   </si>
   <si>
-    <t>8,844,033.0</t>
-  </si>
-  <si>
-    <t>7,411,598.7</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>7,352,170.7</t>
-  </si>
-  <si>
-    <t>PCBL</t>
-  </si>
-  <si>
-    <t>5,246,482.59</t>
-  </si>
-  <si>
-    <t>HPPL</t>
-  </si>
-  <si>
-    <t>4,175,850.4</t>
-  </si>
-  <si>
     <t>Top Traded Stocks</t>
   </si>
   <si>
@@ -518,109 +512,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>201,906,229.4</t>
-  </si>
-  <si>
-    <t>174,541,813.4</t>
-  </si>
-  <si>
-    <t>131,233,809.7</t>
-  </si>
-  <si>
-    <t>107,594,176.7</t>
-  </si>
-  <si>
-    <t>99,891,645.3</t>
+    <t>189,620,303.4</t>
+  </si>
+  <si>
+    <t>187,670,739.2</t>
+  </si>
+  <si>
+    <t>171,744,772.0</t>
+  </si>
+  <si>
+    <t>112,766,108.8</t>
+  </si>
+  <si>
+    <t>107,889,373.5</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>1,306,723,287.0</t>
+    <t>1,351,595,520.7</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>867,868,001.4</t>
+    <t>875,167,390.5</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>446,566,071.4</t>
+    <t>445,464,420.4</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>373,355,391.12</t>
+    <t>366,337,332.02</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>334,400,016.7</t>
+    <t>340,727,446.1</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>329,275,150.3</t>
+    <t>330,945,551.7</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>306,353,856.6</t>
+    <t>296,421,173.0</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>121,176,315.1</t>
+    <t>153,647,883.0</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>107,810,143.7</t>
+    <t>96,638,369.2</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>65,261,148.1</t>
+    <t>68,031,929.9</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>35,841,176.4</t>
+    <t>36,092,606.79</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>22,517,918.6</t>
+    <t>24,057,326.3</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>18,906,479.89</t>
+    <t>15,638,677.9</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>9,042,866.5</t>
+    <t>9,627,863.69</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>2,920,274.59</t>
+    <t>2,926,799.59</t>
   </si>
   <si>
     <t>Total</t>
@@ -632,214 +626,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>110,399,427.3</t>
-  </si>
-  <si>
-    <t>51,405,385.8</t>
-  </si>
-  <si>
-    <t>40,228,218.7</t>
-  </si>
-  <si>
-    <t>37,587,731.79</t>
-  </si>
-  <si>
-    <t>34,081,493.2</t>
-  </si>
-  <si>
-    <t>106,080,111.6</t>
-  </si>
-  <si>
-    <t>48,471,788.8</t>
-  </si>
-  <si>
-    <t>20,957,959.39</t>
-  </si>
-  <si>
-    <t>13,857,450.0</t>
-  </si>
-  <si>
-    <t>8,559,937.5</t>
-  </si>
-  <si>
-    <t>40,689,428.7</t>
-  </si>
-  <si>
-    <t>34,878,270.5</t>
-  </si>
-  <si>
-    <t>11,153,489.3</t>
-  </si>
-  <si>
-    <t>10,291,787.92</t>
-  </si>
-  <si>
-    <t>9,637,786.1</t>
-  </si>
-  <si>
-    <t>36,925,423.5</t>
-  </si>
-  <si>
-    <t>31,244,059.3</t>
-  </si>
-  <si>
-    <t>13,290,515.2</t>
-  </si>
-  <si>
-    <t>11,279,195.0</t>
-  </si>
-  <si>
-    <t>9,919,216.69</t>
-  </si>
-  <si>
-    <t>32,168,498.9</t>
-  </si>
-  <si>
-    <t>26,812,445.8</t>
-  </si>
-  <si>
-    <t>16,166,638.9</t>
-  </si>
-  <si>
-    <t>16,129,995.9</t>
-  </si>
-  <si>
-    <t>15,909,734.6</t>
-  </si>
-  <si>
-    <t>33,134,499.1</t>
-  </si>
-  <si>
-    <t>20,249,607.2</t>
-  </si>
-  <si>
-    <t>14,105,910.2</t>
-  </si>
-  <si>
-    <t>11,523,766.3</t>
-  </si>
-  <si>
-    <t>7,575,838.6</t>
-  </si>
-  <si>
-    <t>37,375,181.5</t>
-  </si>
-  <si>
-    <t>27,341,133.5</t>
-  </si>
-  <si>
-    <t>12,161,495.7</t>
-  </si>
-  <si>
-    <t>11,266,924.3</t>
-  </si>
-  <si>
-    <t>8,886,558.19</t>
-  </si>
-  <si>
-    <t>120,761,548.2</t>
-  </si>
-  <si>
-    <t>106,983,141.7</t>
-  </si>
-  <si>
-    <t>76,174,100.5</t>
-  </si>
-  <si>
-    <t>67,167,088.0</t>
-  </si>
-  <si>
-    <t>44,063,119.4</t>
-  </si>
-  <si>
-    <t>44,903,590.1</t>
-  </si>
-  <si>
-    <t>28,344,260.1</t>
-  </si>
-  <si>
-    <t>21,709,641.6</t>
-  </si>
-  <si>
-    <t>11,851,913.1</t>
-  </si>
-  <si>
-    <t>10,344,276.3</t>
-  </si>
-  <si>
-    <t>94,825,986.1</t>
-  </si>
-  <si>
-    <t>25,402,105.3</t>
-  </si>
-  <si>
-    <t>20,056,952.5</t>
-  </si>
-  <si>
-    <t>13,001,290.3</t>
-  </si>
-  <si>
-    <t>7,654,824.2</t>
-  </si>
-  <si>
-    <t>58,252,440.1</t>
-  </si>
-  <si>
-    <t>32,572,617.4</t>
-  </si>
-  <si>
-    <t>15,319,510.4</t>
-  </si>
-  <si>
-    <t>11,799,105.5</t>
-  </si>
-  <si>
-    <t>9,523,501.9</t>
-  </si>
-  <si>
-    <t>32,627,824.3</t>
-  </si>
-  <si>
-    <t>27,264,549.1</t>
-  </si>
-  <si>
-    <t>14,691,541.8</t>
-  </si>
-  <si>
-    <t>14,614,814.2</t>
-  </si>
-  <si>
-    <t>11,469,846.5</t>
-  </si>
-  <si>
-    <t>36,152,344.4</t>
-  </si>
-  <si>
-    <t>30,424,744.9</t>
-  </si>
-  <si>
-    <t>17,482,601.3</t>
-  </si>
-  <si>
-    <t>11,493,416.2</t>
-  </si>
-  <si>
-    <t>9,819,005.6</t>
-  </si>
-  <si>
-    <t>37,235,431.29</t>
-  </si>
-  <si>
-    <t>18,733,391.0</t>
-  </si>
-  <si>
-    <t>11,154,408.2</t>
-  </si>
-  <si>
-    <t>10,693,372.6</t>
-  </si>
-  <si>
-    <t>10,112,470.19</t>
+    <t>108,744,422.7</t>
+  </si>
+  <si>
+    <t>47,045,901.9</t>
+  </si>
+  <si>
+    <t>39,715,267.2</t>
+  </si>
+  <si>
+    <t>38,778,606.4</t>
+  </si>
+  <si>
+    <t>35,191,748.2</t>
+  </si>
+  <si>
+    <t>146,293,975.1</t>
+  </si>
+  <si>
+    <t>48,421,939.3</t>
+  </si>
+  <si>
+    <t>11,829,453.0</t>
+  </si>
+  <si>
+    <t>11,312,199.5</t>
+  </si>
+  <si>
+    <t>11,290,262.0</t>
+  </si>
+  <si>
+    <t>42,098,327.0</t>
+  </si>
+  <si>
+    <t>25,977,716.4</t>
+  </si>
+  <si>
+    <t>12,129,404.9</t>
+  </si>
+  <si>
+    <t>10,681,870.92</t>
+  </si>
+  <si>
+    <t>9,964,650.1</t>
+  </si>
+  <si>
+    <t>33,665,651.9</t>
+  </si>
+  <si>
+    <t>28,762,238.0</t>
+  </si>
+  <si>
+    <t>19,546,086.8</t>
+  </si>
+  <si>
+    <t>16,040,922.6</t>
+  </si>
+  <si>
+    <t>15,805,240.4</t>
+  </si>
+  <si>
+    <t>39,396,765.5</t>
+  </si>
+  <si>
+    <t>32,952,937.2</t>
+  </si>
+  <si>
+    <t>13,817,200.2</t>
+  </si>
+  <si>
+    <t>11,334,042.0</t>
+  </si>
+  <si>
+    <t>10,237,234.69</t>
+  </si>
+  <si>
+    <t>35,886,426.4</t>
+  </si>
+  <si>
+    <t>19,389,559.5</t>
+  </si>
+  <si>
+    <t>9,781,520.3</t>
+  </si>
+  <si>
+    <t>8,895,865.5</t>
+  </si>
+  <si>
+    <t>7,890,737.9</t>
+  </si>
+  <si>
+    <t>33,816,751.6</t>
+  </si>
+  <si>
+    <t>20,610,856.2</t>
+  </si>
+  <si>
+    <t>16,195,790.2</t>
+  </si>
+  <si>
+    <t>11,396,056.3</t>
+  </si>
+  <si>
+    <t>9,248,984.6</t>
+  </si>
+  <si>
+    <t>106,824,206.7</t>
+  </si>
+  <si>
+    <t>97,209,753.2</t>
+  </si>
+  <si>
+    <t>80,900,817.4</t>
+  </si>
+  <si>
+    <t>67,247,802.2</t>
+  </si>
+  <si>
+    <t>44,284,963.5</t>
+  </si>
+  <si>
+    <t>66,305,258.3</t>
+  </si>
+  <si>
+    <t>28,749,005.5</t>
+  </si>
+  <si>
+    <t>19,473,981.6</t>
+  </si>
+  <si>
+    <t>12,589,841.1</t>
+  </si>
+  <si>
+    <t>10,825,918.6</t>
+  </si>
+  <si>
+    <t>98,232,733.6</t>
+  </si>
+  <si>
+    <t>26,866,745.7</t>
+  </si>
+  <si>
+    <t>20,483,370.5</t>
+  </si>
+  <si>
+    <t>13,143,720.0</t>
+  </si>
+  <si>
+    <t>8,031,662.8</t>
+  </si>
+  <si>
+    <t>45,050,317.3</t>
+  </si>
+  <si>
+    <t>26,807,813.2</t>
+  </si>
+  <si>
+    <t>15,438,394.3</t>
+  </si>
+  <si>
+    <t>15,124,070.7</t>
+  </si>
+  <si>
+    <t>10,696,921.5</t>
+  </si>
+  <si>
+    <t>45,970,496.8</t>
+  </si>
+  <si>
+    <t>29,296,041.4</t>
+  </si>
+  <si>
+    <t>16,014,333.1</t>
+  </si>
+  <si>
+    <t>11,921,986.5</t>
+  </si>
+  <si>
+    <t>8,441,774.9</t>
+  </si>
+  <si>
+    <t>41,389,745.79</t>
+  </si>
+  <si>
+    <t>31,383,143.8</t>
+  </si>
+  <si>
+    <t>14,287,170.9</t>
+  </si>
+  <si>
+    <t>10,313,861.9</t>
+  </si>
+  <si>
+    <t>9,591,443.3</t>
+  </si>
+  <si>
+    <t>37,198,998.2</t>
+  </si>
+  <si>
+    <t>30,403,479.7</t>
+  </si>
+  <si>
+    <t>17,073,277.3</t>
+  </si>
+  <si>
+    <t>12,439,820.2</t>
+  </si>
+  <si>
+    <t>9,770,605.6</t>
   </si>
 </sst>
 </file>
@@ -1648,7 +1642,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1178515627810793</v>
+        <v>0.1220496666352299</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1657,52 +1651,52 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.161859509985331</v>
+        <v>0.2598084837213419</v>
       </c>
       <c r="H9" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="13" t="s">
-        <v>74</v>
-      </c>
       <c r="J9" s="14">
-        <v>0.04738628204761337</v>
+        <v>0.02524238101099703</v>
       </c>
       <c r="K9" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="15" t="s">
-        <v>83</v>
-      </c>
       <c r="M9" s="16">
-        <v>0.04189471273514429</v>
+        <v>0.02838734580108786</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P9" s="18">
-        <v>0.02029011266782151</v>
+        <v>0.0436835267301325</v>
       </c>
       <c r="Q9" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="S9" s="16">
+        <v>0.02386661027484183</v>
+      </c>
+      <c r="T9" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="R9" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="S9" s="16">
-        <v>0.04210055053902215</v>
-      </c>
-      <c r="T9" s="17" t="s">
-        <v>85</v>
-      </c>
       <c r="U9" s="17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="V9" s="18">
-        <v>0.06493214182975049</v>
+        <v>0.04960555368148835</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1714,7 +1708,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.04145435408427833</v>
+        <v>0.04227858898786282</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1723,52 +1717,52 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.04377487724348732</v>
+        <v>0.01764090085555953</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.01736728514576292</v>
+        <v>0.01616909106936964</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M10" s="16">
-        <v>0.02587237043445507</v>
+        <v>0.01757643390922629</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P10" s="18">
-        <v>0.01569844810963906</v>
+        <v>0.01840484163284105</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S10" s="16">
-        <v>0.03037750958179183</v>
+        <v>0.01937080655911995</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="V10" s="18">
-        <v>0.04238905927495795</v>
+        <v>0.02947324456565945</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1780,16 +1774,16 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.03886453651368078</v>
+        <v>0.04148892099552132</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.04210619381480158</v>
+        <v>0.01535906151767883</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>76</v>
@@ -1798,43 +1792,43 @@
         <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.01646363186636109</v>
+        <v>0.01446032796827861</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M11" s="16">
-        <v>0.01738366837436696</v>
+        <v>0.01441621008552886</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P11" s="18">
-        <v>0.01213137045860694</v>
+        <v>0.01789165155164498</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01745717858535343</v>
+        <v>0.01885541023309797</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V11" s="18">
-        <v>0.03644248104940316</v>
+        <v>0.01722811733032858</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1846,16 +1840,16 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01312181856373148</v>
+        <v>0.01375828529775497</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="12">
-        <v>0.02023302650851871</v>
+        <v>0.01424407090008429</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>78</v>
@@ -1864,43 +1858,43 @@
         <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01131737737596466</v>
+        <v>0.01014860421254263</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01214589171062306</v>
+        <v>0.01186775299989062</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01192774939671934</v>
+        <v>0.0142362697210385</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01505449874976745</v>
+        <v>0.01848701287191486</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V12" s="18">
-        <v>0.02639458621466271</v>
+        <v>0.01425125579187045</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1912,7 +1906,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01022401197442652</v>
+        <v>0.01085794360055527</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>71</v>
@@ -1921,52 +1915,52 @@
         <v>72</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01196462260084956</v>
+        <v>0.009957138786578824</v>
       </c>
       <c r="H13" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="13" t="s">
-        <v>81</v>
-      </c>
       <c r="J13" s="14">
-        <v>0.00996288482769475</v>
+        <v>0.009751935939765354</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01208360904135515</v>
+        <v>0.01095349934908947</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01191822091302288</v>
+        <v>0.01297623233165491</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01238959161871366</v>
+        <v>0.01233068863002695</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01786963748364032</v>
+        <v>0.01189855310973563</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1977,7 +1971,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1986,7 +1980,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -1995,7 +1989,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2004,7 +1998,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2013,7 +2007,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2022,7 +2016,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2031,7 +2025,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2040,49 +2034,49 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1329914184790703</v>
+        <v>0.1224189913778199</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>64</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G16" s="12">
-        <v>0.02672530889816661</v>
+        <v>0.07815885130902644</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>64</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J16" s="14">
-        <v>0.165251980947164</v>
+        <v>0.1632154873025556</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="L16" s="15" t="s">
         <v>135</v>
       </c>
       <c r="M16" s="16">
-        <v>0.03316307983345031</v>
+        <v>0.04631800743096245</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P16" s="18">
-        <v>0.0373578908225541</v>
+        <v>0.02600704795538358</v>
       </c>
       <c r="Q16" s="15" t="s">
         <v>147</v>
@@ -2091,82 +2085,82 @@
         <v>148</v>
       </c>
       <c r="S16" s="16">
-        <v>0.04301234890584673</v>
+        <v>0.02864491567448501</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="U16" s="17" t="s">
         <v>154</v>
       </c>
       <c r="V16" s="18">
-        <v>0.03960366768316095</v>
+        <v>0.04148014785056661</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1182135514256691</v>
+        <v>0.1094466142254545</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G17" s="12">
-        <v>0.01410953391908855</v>
+        <v>0.01230191088219051</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J17" s="14">
-        <v>0.02228192966984057</v>
+        <v>0.02188329725527159</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="L17" s="15" t="s">
         <v>136</v>
       </c>
       <c r="M17" s="16">
-        <v>0.03238386411253722</v>
+        <v>0.03727320570626018</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="O17" s="17" t="s">
         <v>142</v>
       </c>
       <c r="P17" s="18">
-        <v>0.02883144552713215</v>
+        <v>0.01694956004926821</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="R17" s="15" t="s">
         <v>149</v>
       </c>
       <c r="S17" s="16">
-        <v>0.03026867249761298</v>
+        <v>0.02833628627385716</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="U17" s="17" t="s">
         <v>155</v>
       </c>
       <c r="V17" s="18">
-        <v>0.03318921264944938</v>
+        <v>0.02976469298882328</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2175,204 +2169,204 @@
         <v>58</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D18" s="10">
-        <v>0.05057569487571795</v>
+        <v>0.05262481239357203</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G18" s="12">
-        <v>0.01305101752521973</v>
+        <v>0.0113790048231112</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>131</v>
       </c>
       <c r="J18" s="14">
-        <v>0.01873715083587199</v>
+        <v>0.01849905083744276</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M18" s="16">
-        <v>0.02441585973865263</v>
+        <v>0.02647651365827746</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P18" s="18">
-        <v>0.02492389377339362</v>
+        <v>0.01374024110939114</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="R18" s="15" t="s">
         <v>150</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02313170735591804</v>
+        <v>0.01994674793125564</v>
       </c>
       <c r="T18" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="U18" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="U18" s="17" t="s">
-        <v>157</v>
-      </c>
       <c r="V18" s="18">
-        <v>0.0329230934747386</v>
+        <v>0.02244313235377546</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D19" s="10">
-        <v>0.04796842108822578</v>
+        <v>0.04970310247988003</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01240663453664156</v>
+        <v>0.01094878021568882</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01073836698993031</v>
+        <v>0.0111166751784515</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01615921135397573</v>
+        <v>0.02325551485281076</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01630945594581726</v>
+        <v>0.01266769045429913</v>
       </c>
       <c r="Q19" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="R19" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="R19" s="15" t="s">
-        <v>152</v>
-      </c>
       <c r="S19" s="16">
-        <v>0.01599014208767179</v>
+        <v>0.01866631885381187</v>
       </c>
       <c r="T19" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="U19" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="U19" s="17" t="s">
-        <v>159</v>
-      </c>
       <c r="V19" s="18">
-        <v>0.02349380123252437</v>
+        <v>0.01595267537855401</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D20" s="10">
-        <v>0.02389595182864752</v>
+        <v>0.02485615781459533</v>
       </c>
       <c r="E20" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>128</v>
-      </c>
       <c r="G20" s="12">
-        <v>0.01144928833956008</v>
+        <v>0.005679299628132316</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01018386488500781</v>
+        <v>0.01091021397903991</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01185134852706511</v>
+        <v>0.01497731123824987</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="O20" s="17" t="s">
         <v>146</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01466042567885042</v>
+        <v>0.01092865806079166</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01482108293764071</v>
+        <v>0.0149785828877391</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01869949959890412</v>
+        <v>0.01437989513172069</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2380,226 +2374,226 @@
         <v>56</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" s="19" t="s">
         <v>164</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2960862119436544</v>
+        <v>0.3062536665454513</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D32" s="22">
-        <v>0.1966474092549298</v>
+        <v>0.1983013542711571</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1011859647553564</v>
+        <v>0.1009363452110206</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D34" s="22">
-        <v>0.08459739300985021</v>
+        <v>0.08300719365028549</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D35" s="22">
-        <v>0.07577062045470209</v>
+        <v>0.07720433225966124</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D36" s="22">
-        <v>0.07460939351844921</v>
+        <v>0.07498788438018845</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D37" s="22">
-        <v>0.06941573156109485</v>
+        <v>0.06716511684349023</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D38" s="22">
-        <v>0.02745695012263881</v>
+        <v>0.03481457788593906</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D39" s="22">
-        <v>0.02442835248656132</v>
+        <v>0.02189697616128909</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01478731290722212</v>
+        <v>0.01541513541214425</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D41" s="22">
-        <v>0.008121136477366767</v>
+        <v>0.008178107280171076</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D42" s="22">
-        <v>0.005102262495402791</v>
+        <v>0.005451071917462086</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D43" s="22">
-        <v>0.004283958256863789</v>
+        <v>0.00354351754903557</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D44" s="22">
-        <v>0.00204899393294211</v>
+        <v>0.00218154656031841</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D45" s="22">
-        <v>0.0006616955936964245</v>
+        <v>0.0006631740723859469</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="D46" s="20" t="s">
         <v>202</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2978,331 +2972,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1284573930658095</v>
+        <v>0.1310330372788417</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G9" s="12">
-        <v>0.2903868371424891</v>
+        <v>0.3491638776262194</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1328556716351407</v>
+        <v>0.1349967474313075</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>172</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1312304672997525</v>
+        <v>0.114081527559438</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1187038251523257</v>
+        <v>0.1468615225678672</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1478685381010868</v>
+        <v>0.1507395875678633</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1673664342640767</v>
+        <v>0.1464208886470371</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0.05668858470549799</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="D10" s="10">
-        <v>0.05981373283274435</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>174</v>
-      </c>
       <c r="F10" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1326881092786363</v>
+        <v>0.115569982130928</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1138815707370601</v>
+        <v>0.08330276924527034</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1110392817100711</v>
+        <v>0.09746551342046385</v>
       </c>
       <c r="N10" s="17" t="s">
         <v>172</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P10" s="18">
-        <v>0.09893964552226615</v>
+        <v>0.1228405040072468</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="S10" s="16">
-        <v>0.09036743862487547</v>
+        <v>0.08144511714748354</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1224338675822376</v>
+        <v>0.08924156631828276</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D11" s="10">
-        <v>0.04680832345117835</v>
+        <v>0.04785543900410773</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G11" s="12">
-        <v>0.05737093835341232</v>
+        <v>0.02823368273952325</v>
       </c>
       <c r="H11" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="J11" s="14">
+        <v>0.03889537486317125</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="M11" s="16">
+        <v>0.06623508870634306</v>
+      </c>
+      <c r="N11" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="I11" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="J11" s="14">
-        <v>0.03641742731145437</v>
-      </c>
-      <c r="K11" s="15" t="s">
+      <c r="O11" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="P11" s="18">
+        <v>0.051507148702272</v>
+      </c>
+      <c r="Q11" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="L11" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="M11" s="16">
-        <v>0.04723359558355408</v>
-      </c>
-      <c r="N11" s="17" t="s">
+      <c r="R11" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="S11" s="16">
+        <v>0.04108690899935032</v>
+      </c>
+      <c r="T11" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="O11" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="P11" s="18">
-        <v>0.05965593493348819</v>
-      </c>
-      <c r="Q11" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="R11" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="S11" s="16">
-        <v>0.06295010869378764</v>
-      </c>
-      <c r="T11" s="17" t="s">
-        <v>184</v>
-      </c>
       <c r="U11" s="17" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="V11" s="18">
-        <v>0.05445929862914248</v>
+        <v>0.07012506764324977</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0.04672679712550195</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.02699913950114122</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="J12" s="14">
+        <v>0.03425356619708589</v>
+      </c>
+      <c r="K12" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="D12" s="10">
-        <v>0.04373593374867831</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0.03793379376837105</v>
-      </c>
-      <c r="H12" s="13" t="s">
+      <c r="L12" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="M12" s="16">
+        <v>0.05435727070149832</v>
+      </c>
+      <c r="N12" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="I12" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="J12" s="14">
-        <v>0.03360387304818629</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="M12" s="16">
-        <v>0.04008549910375524</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>180</v>
-      </c>
       <c r="O12" s="17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P12" s="18">
-        <v>0.05952071991215387</v>
+        <v>0.04225054122699882</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S12" s="16">
-        <v>0.05142683675575981</v>
+        <v>0.0373667492433625</v>
       </c>
       <c r="T12" s="17" t="s">
         <v>176</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="V12" s="18">
-        <v>0.05045339900795608</v>
+        <v>0.04934302118236768</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D13" s="10">
-        <v>0.03965618187823802</v>
+        <v>0.04240476467027315</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G13" s="12">
-        <v>0.02343222626061402</v>
+        <v>0.02694678066298545</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J13" s="14">
-        <v>0.03146848177279331</v>
+        <v>0.03195365347395047</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M13" s="16">
-        <v>0.03525222785294553</v>
+        <v>0.05355862330044892</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P13" s="18">
-        <v>0.05870794158126868</v>
+        <v>0.0381619114119052</v>
       </c>
       <c r="Q13" s="15" t="s">
         <v>176</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="S13" s="16">
-        <v>0.03380851405934741</v>
+        <v>0.03314474847381593</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="V13" s="18">
-        <v>0.03979409595145891</v>
+        <v>0.04004655917970433</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3313,7 +3307,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3322,7 +3316,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3331,7 +3325,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3340,7 +3334,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3349,7 +3343,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3358,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3367,7 +3361,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3376,67 +3370,67 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1405144396465823</v>
+        <v>0.1287192474911524</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1229204165494278</v>
+        <v>0.1582525943341878</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J16" s="14">
-        <v>0.3096177674222301</v>
+        <v>0.3150030053993859</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M16" s="16">
-        <v>0.2070252474064067</v>
+        <v>0.1526603147293095</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1203987653526476</v>
+        <v>0.1713667877950353</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1613362042752296</v>
+        <v>0.1738560742128032</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="V16" s="18">
-        <v>0.166740631479368</v>
+        <v>0.1610654517515377</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3445,262 +3439,262 @@
         <v>182</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1244823077517187</v>
+        <v>0.1171341839761553</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G17" s="12">
-        <v>0.0775904165016268</v>
+        <v>0.0686160467744205</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J17" s="14">
-        <v>0.08294079981953807</v>
+        <v>0.08615362039361009</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1157608876869903</v>
+        <v>0.09084262765706506</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1006079357101552</v>
+        <v>0.1092084893419809</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1357757827237381</v>
+        <v>0.1318237179780862</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="V17" s="18">
-        <v>0.08388831110679011</v>
+        <v>0.1316419911732785</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D18" s="10">
-        <v>0.08863385081493967</v>
+        <v>0.09748251504822202</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G18" s="12">
-        <v>0.05942861545519913</v>
+        <v>0.04647909063671105</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J18" s="14">
-        <v>0.06548826023063858</v>
+        <v>0.0656840447348512</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M18" s="16">
-        <v>0.05444450782251473</v>
+        <v>0.05231550572792919</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="P18" s="18">
-        <v>0.05421273197939876</v>
+        <v>0.05969752369582201</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="S18" s="16">
-        <v>0.07801918745272837</v>
+        <v>0.06001272528427569</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="V18" s="18">
-        <v>0.04994955079375275</v>
+        <v>0.0739244402878509</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D19" s="10">
-        <v>0.07815356687363738</v>
+        <v>0.08103113294280952</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G19" s="12">
-        <v>0.03244377770051887</v>
+        <v>0.03004852205409754</v>
       </c>
       <c r="H19" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J19" s="14">
+        <v>0.04214798011207962</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M19" s="16">
+        <v>0.0512503691744326</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="O19" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="P19" s="18">
+        <v>0.04444225476894945</v>
+      </c>
+      <c r="Q19" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="R19" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="S19" s="16">
+        <v>0.04332298991570526</v>
+      </c>
+      <c r="T19" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="I19" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="J19" s="14">
-        <v>0.04245071042076194</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="M19" s="16">
-        <v>0.04193322599222404</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="O19" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="P19" s="18">
-        <v>0.05392960221188705</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="R19" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="S19" s="16">
-        <v>0.05129139408904927</v>
-      </c>
-      <c r="T19" s="17" t="s">
-        <v>184</v>
-      </c>
       <c r="U19" s="17" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="V19" s="18">
-        <v>0.04788502879428636</v>
+        <v>0.05386234461069179</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D20" s="10">
-        <v>0.05127049647721766</v>
+        <v>0.05336175528924522</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G20" s="12">
-        <v>0.02831672810273524</v>
+        <v>0.02583851942404299</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02499388275608619</v>
+        <v>0.0257551411595294</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="M20" s="16">
-        <v>0.03384588411469625</v>
+        <v>0.03624825529974052</v>
       </c>
       <c r="N20" s="17" t="s">
         <v>180</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P20" s="18">
-        <v>0.04232446959034245</v>
+        <v>0.0314688756616125</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="S20" s="16">
-        <v>0.04381904187826954</v>
+        <v>0.04028849769289221</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="V20" s="18">
-        <v>0.04528374207295113</v>
+        <v>0.04230509102393257</v>
       </c>
     </row>
   </sheetData>
